--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2294,6 +2294,156 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -2320,37 +2320,37 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:07</t>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>S38/2026</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:07</t>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -2380,37 +2380,37 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:07</t>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>S38/2026</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:07</t>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:07</t>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2444,6 +2444,156 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -2470,37 +2470,37 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09</t>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>S39/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="n">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21 16:09</t>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -2530,37 +2530,37 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09</t>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>S39/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="n">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21 16:09</t>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09</t>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2594,6 +2594,156 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -2620,37 +2620,37 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>S40/2026</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28 17:55</t>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -2680,37 +2680,37 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>S40/2026</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28 17:55</t>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2607,12 +2607,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2697,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -2727,12 +2727,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2744,6 +2744,156 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -2770,37 +2770,37 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:00</t>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>S41/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n">
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05 19:00</t>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -2830,37 +2830,37 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:00</t>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>S41/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n">
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05 19:00</t>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:00</t>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2894,6 +2894,156 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -2920,37 +2920,37 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:34</t>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>S42/2026</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12 19:34</t>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -2980,37 +2980,37 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:34</t>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>S42/2026</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12 19:34</t>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:34</t>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3044,6 +3044,156 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -3070,37 +3070,37 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 16:47</t>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>S43/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19 16:47</t>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -3130,37 +3130,37 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 16:47</t>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>S43/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19 16:47</t>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 16:47</t>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3194,6 +3194,156 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -3220,37 +3220,37 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 16:26</t>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>S44/2026</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>26/10/2026</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26 16:26</t>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -3280,37 +3280,37 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 16:26</t>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>S44/2026</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>26/10/2026</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26 16:26</t>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 16:26</t>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
